--- a/artfynd/A 26693-2026 artfynd.xlsx
+++ b/artfynd/A 26693-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16888684</v>
+        <v>129688267</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>9700 m N Nästräsk, Lu lm</t>
+          <t>Nästräsk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730141.1210880211</v>
+        <v>730141</v>
       </c>
       <c r="R2" t="n">
-        <v>7329535.098233704</v>
+        <v>7329526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16888685</v>
+        <v>16888684</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730143.9231996535</v>
+        <v>730141</v>
       </c>
       <c r="R3" t="n">
-        <v>7329530.828578057</v>
+        <v>7329535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +849,9 @@
           <t>2014-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16888686</v>
+        <v>16888685</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,14 +914,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>9600 m N Nästräsk, Lu lm</t>
+          <t>9700 m N Nästräsk, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730166.9783196996</v>
+        <v>730144</v>
       </c>
       <c r="R4" t="n">
-        <v>7329524.114184896</v>
+        <v>7329531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +951,9 @@
           <t>2014-10-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129688267</v>
+        <v>16888686</v>
       </c>
       <c r="B5" t="n">
-        <v>97061</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,38 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nästräsk, Lu lm</t>
+          <t>9600 m N Nästräsk, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730141</v>
+        <v>730167</v>
       </c>
       <c r="R5" t="n">
-        <v>7329526</v>
+        <v>7329524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,17 +1050,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Sveaskog naturvärdesinventering, inventerare: Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,44 +1075,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129688269</v>
+        <v>129688274</v>
       </c>
       <c r="B6" t="n">
-        <v>92905</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1171,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730218</v>
+        <v>730268</v>
       </c>
       <c r="R6" t="n">
-        <v>7329464</v>
+        <v>7329501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129688273</v>
+        <v>129688269</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,21 +1204,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730273</v>
+        <v>730218</v>
       </c>
       <c r="R7" t="n">
-        <v>7329493</v>
+        <v>7329464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129688274</v>
+        <v>129688273</v>
       </c>
       <c r="B8" t="n">
-        <v>78755</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730268</v>
+        <v>730273</v>
       </c>
       <c r="R8" t="n">
-        <v>7329501</v>
+        <v>7329493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1408,7 @@
         <v>129688268</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>79917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26693-2026 artfynd.xlsx
+++ b/artfynd/A 26693-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16888684</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16888685</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16888686</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688268</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688274</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688269</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,8 +1548,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>